--- a/data_src/xlsx表/商城上架表.xlsx
+++ b/data_src/xlsx表/商城上架表.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,45 +424,40 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>currencytype</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>itemid</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>shopdesc</t>
-        </is>
-      </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>shopicon</t>
+          <t>conditionid</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>conditionid</t>
+          <t>stocklimit</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>stocklimit</t>
+          <t>shoptab</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>shoptab</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
         <is>
           <t>tutorialonly</t>
         </is>
@@ -471,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -491,12 +486,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -510,11 +505,6 @@
         </is>
       </c>
       <c r="I2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
@@ -523,53 +513,79 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>上架 id</t>
+          <t>上架id</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>22饭圈积分/23星星/24情报点</t>
+          <t>名称</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>售价</t>
+          <t>货币类型</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>购买后给的道具</t>
+          <t>价格</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>商城展示描述</t>
+          <t>道具id</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>art/icons 展示图</t>
+          <t>条件id</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>显示条件；0=无条件</t>
+          <t>库存上限</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1=无限</t>
+          <t>商城页签</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1周边售卖/2周边兑换</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0/1</t>
-        </is>
+          <t>教程专用</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>教程专辑</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>22</v>
+      </c>
+      <c r="D4" t="n">
+        <v>50</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1001</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data_src/xlsx表/商城上架表.xlsx
+++ b/data_src/xlsx表/商城上架表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,6 +462,16 @@
           <t>tutorialonly</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>shopdesc</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>shopicon</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -509,6 +519,16 @@
           <t>int</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -554,6 +574,16 @@
       <c r="I3" t="inlineStr">
         <is>
           <t>教程专用</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>商城展示描述</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>展示图标路径</t>
         </is>
       </c>
     </row>
@@ -579,7 +609,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
@@ -587,6 +617,48 @@
       <c r="I4" t="n">
         <v>1</v>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>新手教程专用普通专辑，购买后可在会员区升级。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>普通专辑</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>22</v>
+      </c>
+      <c r="D5" t="n">
+        <v>80</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1002</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>常规普通专辑，购买后可在会员区升级。</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
